--- a/data/trans_orig/IP09B02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>36256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58325</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70687</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31576</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72284</t>
+          <t>72400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>98413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114986</t>
+          <t>114016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2012 (tasa de respuesta: 97,74%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2012 (tasa de respuesta: 97,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,81%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48492</t>
+          <t>48172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66897</t>
+          <t>66629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84710</t>
+          <t>84604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37439</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55252</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58425</t>
+          <t>58200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70547</t>
+          <t>69358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102383</t>
+          <t>102009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123457</t>
+          <t>122446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57070</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27592</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44342</t>
+          <t>43668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38540</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60958</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>28590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>53233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34556</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40106</t>
+          <t>41295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56268</t>
+          <t>56200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72617</t>
+          <t>70640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88752</t>
+          <t>88032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30773</t>
+          <t>32750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64030</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82179</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113774</t>
+          <t>114571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>135763</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48804</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP09B02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6048</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5226</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7178</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7156</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>66,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8963</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6183</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>86,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4319</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2592</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4899</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5416</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4184</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36062</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45506</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>23684</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19414</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27023</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19561</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27132</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>77,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36256</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>45987</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58529</t>
+          <t>59080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71112</t>
+          <t>70930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11370</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7261</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16705</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6876</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3537</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11146</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3428</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10999</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>11370</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16511</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>52767</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52767</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52767</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30560</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30560</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30560</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>52767</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>52767</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>52767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16969</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13699</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18350</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>72,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10486</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6476</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13585</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7065</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13685</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>60,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16969</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14117</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18351</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31271</t>
+          <t>31484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5297</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6710</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18996</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18996</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18996</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17196</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>17196</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>17196</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18996</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18996</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>72241</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>74,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>39396</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33479</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>44264</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32809</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>44199</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>67331</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>61042</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>72400</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>98818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>114513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14800</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16178</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22095</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22765</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>39,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>14800</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>9731</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21089</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>55574</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>55574</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>55574</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2331,67 +2331,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9705</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>84,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>6703</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3551</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9348</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3934</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9425</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,59%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9573</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>60,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4555</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7520</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>65,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6043</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3398</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9195</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8812</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>47,41%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4555</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7587</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>39,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42472</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36044</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>33403</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27413</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38590</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26970</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39141</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>61,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>50,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>42472</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36001</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>48172</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>62,56%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66629</t>
+          <t>66430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84604</t>
+          <t>84097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25421</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19218</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31849</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>37,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20853</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15666</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26843</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15115</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27286</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>38,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>25421</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>19721</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>31892</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55520</t>
+          <t>55719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67893</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67893</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67893</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54256</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>54256</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>54256</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67893</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67893</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67893</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>12538</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8579</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15869</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>11168</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7840</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13692</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7740</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13351</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>73,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12538</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8880</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15974</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2971</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10261</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4072</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1548</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>26,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6302</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2866</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9960</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14884</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18840</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18840</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18840</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18840</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18840</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>54369</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69759</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>55,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51274</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>44459</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>58200</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43562</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57908</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>70,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>62007</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>54405</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>69358</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>63,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102009</t>
+          <t>101791</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122446</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36277</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28525</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43915</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>30968</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37783</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24334</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38680</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>37,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>36277</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>28926</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>43879</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58081</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>82242</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2485</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3909</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>55,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>1964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3767</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3814</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2129</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,77%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22521</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17399</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27269</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>58,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14854</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10183</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9963</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19535</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>47,8%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22521</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17386</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27278</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>58,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>31058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43668</t>
+          <t>44172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15994</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11246</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21116</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>54,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16223</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11474</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20894</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>21114</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>52,2%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15994</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11237</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>21129</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>41,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3080</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8004</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6853</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4237</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9394</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>59,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5263</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2673</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8023</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,81%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16137</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4896</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2155</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7079</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>48,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4744</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2203</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7360</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7706</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>63,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4896</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2136</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7486</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>48,19%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22300</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34394</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24192</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18533</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29516</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18689</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29474</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>51,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22748</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>34242</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>44687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23018</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17053</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29147</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>22931</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17607</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28590</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17649</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28434</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>48,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23018</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17205</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28699</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53233</t>
+          <t>53883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,74 +5532,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6458</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>66,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7850</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3954</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>65,98%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9562</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6902</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10908</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>63,27%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43243</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37007</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50565</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>31468</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27170</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34637</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>31355</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41295</t>
+          <t>26623</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56200</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79885</t>
+          <t>74598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70640</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88032</t>
+          <t>82086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16184</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22420</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6105</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2936</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10403</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17400</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13775</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10021</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16599</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12222</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8491</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14750</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,66%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>88,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31881</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3180</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9758</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4371</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1843</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8102</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65683</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58089</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>73728</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>45687</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56596</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>51248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>124989</t>
+          <t>112525</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135763</t>
+          <t>121641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23188</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15143</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30782</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12008</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17861</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
